--- a/table-1b.xlsx
+++ b/table-1b.xlsx
@@ -351,23 +351,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>HFNC/NonInvasiveVent(N=366)</t>
+          <t>HFNC/NonInvasiveVent(N=308)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tracheostomy/InvasiveVent(N=1532)</t>
+          <t>Tracheostomy/InvasiveVent(N=1336)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Overall(N=1898)</t>
+          <t>Overall(N=1644)</t>
         </is>
       </c>
     </row>
@@ -386,17 +386,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.6 (13.3)</t>
+          <t>61.2 (13.3)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62.3 (14.2)</t>
+          <t>56.0 (13.8)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>63.5 (14.3)</t>
+          <t>57.0 (13.9)</t>
         </is>
       </c>
     </row>
@@ -408,17 +408,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>69.0 [9.00, 112]</t>
+          <t>62.0 [4.00, 100]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>62.0 [1.00, 116]</t>
+          <t>57.0 [1.00, 107]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>63.0 [1.00, 116]</t>
+          <t>58.0 [1.00, 107]</t>
         </is>
       </c>
     </row>
@@ -459,17 +459,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.3 (1.71)</t>
+          <t>13.9 (2.13)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14.2 (2.47)</t>
+          <t>13.5 (3.10)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.2 (2.34)</t>
+          <t>13.6 (2.94)</t>
         </is>
       </c>
     </row>
@@ -503,17 +503,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9 (2.5%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17 (1.1%)</t>
+          <t>5 (0.4%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26 (1.4%)</t>
+          <t>5 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -532,17 +532,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.968 (0.915)</t>
+          <t>1.20 (2.09)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.17 (3.61)</t>
+          <t>2.20 (3.82)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.95 (3.33)</t>
+          <t>2.00 (3.56)</t>
         </is>
       </c>
     </row>
@@ -554,17 +554,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.600 [0.200, 7.60]</t>
+          <t>0.600 [0.200, 20.2]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.850 [0.200, 31.9]</t>
+          <t>0.900 [0.200, 36.1]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.800 [0.200, 31.9]</t>
+          <t>0.800 [0.200, 36.1]</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>209 (57.1%)</t>
+          <t>101 (32.8%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>800 (52.2%)</t>
+          <t>505 (37.8%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1009 (53.2%)</t>
+          <t>606 (36.9%)</t>
         </is>
       </c>
     </row>
@@ -605,17 +605,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.37 (1.17)</t>
+          <t>1.41 (1.29)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.46 (1.24)</t>
+          <t>1.54 (1.27)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.44 (1.23)</t>
+          <t>1.52 (1.27)</t>
         </is>
       </c>
     </row>
@@ -627,17 +627,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.00 [0.200, 9.20]</t>
+          <t>1.00 [0.200, 9.70]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.10 [0.300, 9.80]</t>
+          <t>1.10 [0.300, 10.0]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.00 [0.200, 9.80]</t>
+          <t>1.10 [0.200, 10.0]</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>92 (25.1%)</t>
+          <t>9 (2.9%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>203 (13.3%)</t>
+          <t>23 (1.7%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>295 (15.5%)</t>
+          <t>32 (1.9%)</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>215 (141)</t>
+          <t>206 (143)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>195 (117)</t>
+          <t>174 (106)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>198 (121)</t>
+          <t>180 (115)</t>
         </is>
       </c>
     </row>
@@ -700,17 +700,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>199 [5.00, 738]</t>
+          <t>190 [5.00, 778]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>174 [7.00, 909]</t>
+          <t>158 [5.00, 909]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>176 [5.00, 909]</t>
+          <t>162 [5.00, 909]</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>126 (34.4%)</t>
+          <t>12 (3.9%)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>211 (13.8%)</t>
+          <t>24 (1.8%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>337 (17.8%)</t>
+          <t>36 (2.2%)</t>
         </is>
       </c>
     </row>
@@ -751,17 +751,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4 (1.1%)</t>
+          <t>2 (0.6%)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>44 (2.9%)</t>
+          <t>33 (2.5%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48 (2.5%)</t>
+          <t>35 (2.1%)</t>
         </is>
       </c>
     </row>
@@ -773,17 +773,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1 (0.3%)</t>
+          <t>5 (1.6%)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14 (0.9%)</t>
+          <t>58 (4.3%)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15 (0.8%)</t>
+          <t>63 (3.8%)</t>
         </is>
       </c>
     </row>
@@ -795,17 +795,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>361 (98.6%)</t>
+          <t>301 (97.7%)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1474 (96.2%)</t>
+          <t>1245 (93.2%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1835 (96.7%)</t>
+          <t>1546 (94.0%)</t>
         </is>
       </c>
     </row>
@@ -824,17 +824,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7.39 (0.0831)</t>
+          <t>7.41 (0.0757)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7.36 (0.0939)</t>
+          <t>7.40 (0.0818)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.36 (0.0927)</t>
+          <t>7.40 (0.0808)</t>
         </is>
       </c>
     </row>
@@ -846,17 +846,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7.40 [7.04, 7.61]</t>
+          <t>7.42 [7.12, 7.61]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7.37 [6.77, 7.72]</t>
+          <t>7.40 [6.77, 7.72]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.37 [6.77, 7.72]</t>
+          <t>7.41 [6.77, 7.72]</t>
         </is>
       </c>
     </row>
@@ -868,17 +868,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93 (25.4%)</t>
+          <t>52 (16.9%)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>257 (16.8%)</t>
+          <t>157 (11.8%)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>350 (18.4%)</t>
+          <t>209 (12.7%)</t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>23.6 (5.42)</t>
+          <t>24.9 (5.26)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22.1 (5.05)</t>
+          <t>23.2 (4.52)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22.3 (5.15)</t>
+          <t>23.5 (4.71)</t>
         </is>
       </c>
     </row>
@@ -919,17 +919,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23.0 [6.00, 43.0]</t>
+          <t>24.0 [11.0, 45.0]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>22.0 [3.00, 47.0]</t>
+          <t>23.0 [3.00, 47.0]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22.0 [3.00, 47.0]</t>
+          <t>23.0 [3.00, 47.0]</t>
         </is>
       </c>
     </row>
@@ -941,17 +941,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>76 (20.8%)</t>
+          <t>9 (2.9%)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>182 (11.9%)</t>
+          <t>21 (1.6%)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>258 (13.6%)</t>
+          <t>30 (1.8%)</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.45 (0.805)</t>
+          <t>4.57 (0.846)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4.52 (0.823)</t>
+          <t>4.68 (0.813)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.50 (0.820)</t>
+          <t>4.66 (0.820)</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.40 [2.90, 8.70]</t>
+          <t>4.40 [3.20, 9.80]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4.40 [2.60, 8.60]</t>
+          <t>4.50 [3.00, 8.80]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.40 [2.60, 8.70]</t>
+          <t>4.50 [3.00, 9.80]</t>
         </is>
       </c>
     </row>
@@ -1014,24 +1014,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>75 (20.5%)</t>
+          <t>8 (2.6%)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>212 (13.8%)</t>
+          <t>21 (1.6%)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>287 (15.1%)</t>
+          <t>29 (1.8%)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>so2</t>
+          <t>min_spo2_preicu</t>
         </is>
       </c>
     </row>
@@ -1043,17 +1043,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93.7 (3.92)</t>
+          <t>94.3 (3.55)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>96.5 (2.95)</t>
+          <t>97.4 (3.41)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>96.2 (3.15)</t>
+          <t>96.8 (3.65)</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>95.0 [88.0, 98.0]</t>
+          <t>94.0 [86.0, 100]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>97.0 [79.0, 99.0]</t>
+          <t>99.0 [84.0, 100]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>97.0 [79.0, 99.0]</t>
+          <t>98.0 [84.0, 100]</t>
         </is>
       </c>
     </row>
@@ -1087,24 +1087,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>356 (97.3%)</t>
+          <t>269 (87.3%)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1440 (94.0%)</t>
+          <t>1180 (88.3%)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1796 (94.6%)</t>
+          <t>1449 (88.1%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>po2</t>
+          <t>min_resp_rate_preicu</t>
         </is>
       </c>
     </row>
@@ -1116,17 +1116,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>99.5 (54.2)</t>
+          <t>25.1 (7.31)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>209 (107)</t>
+          <t>20.0 (5.89)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>193 (108)</t>
+          <t>20.5 (6.21)</t>
         </is>
       </c>
     </row>
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>81.0 [33.0, 359]</t>
+          <t>25.5 [8.00, 40.0]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>195 [35.0, 563]</t>
+          <t>19.0 [8.00, 42.0]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>172 [33.0, 563]</t>
+          <t>19.0 [8.00, 42.0]</t>
         </is>
       </c>
     </row>
@@ -1160,24 +1160,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>289 (79.0%)</t>
+          <t>268 (87.0%)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1078 (70.4%)</t>
+          <t>950 (71.1%)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1367 (72.0%)</t>
+          <t>1218 (74.1%)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pco2</t>
+          <t>min_so2_preicu</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>41.0 (10.4)</t>
+          <t>93.3 (3.94)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>43.6 (16.9)</t>
+          <t>96.3 (2.85)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>43.2 (16.1)</t>
+          <t>96.0 (3.02)</t>
         </is>
       </c>
     </row>
@@ -1211,17 +1211,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>41.0 [21.0, 79.0]</t>
+          <t>94.0 [88.0, 98.0]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>41.0 [16.0, 162]</t>
+          <t>97.0 [79.0, 99.0]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>41.0 [16.0, 162]</t>
+          <t>97.0 [79.0, 99.0]</t>
         </is>
       </c>
     </row>
@@ -1233,24 +1233,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>289 (79.0%)</t>
+          <t>299 (97.1%)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1078 (70.4%)</t>
+          <t>1220 (91.3%)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1367 (72.0%)</t>
+          <t>1519 (92.4%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fio2</t>
+          <t>min_pao2fio2ratio_preicu</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>85.3 (23.7)</t>
+          <t>134 (95.1)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>57.5 (20.2)</t>
+          <t>324 (130)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>59.2 (21.3)</t>
+          <t>309 (137)</t>
         </is>
       </c>
     </row>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>95.5 [50.0, 100]</t>
+          <t>114 [65.6, 342]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>50.0 [29.0, 100]</t>
+          <t>323 [64.1, 575]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>50.0 [29.0, 100]</t>
+          <t>313 [64.1, 575]</t>
         </is>
       </c>
     </row>
@@ -1306,24 +1306,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>362 (98.9%)</t>
+          <t>301 (97.7%)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1471 (96.0%)</t>
+          <t>1251 (93.6%)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1833 (96.6%)</t>
+          <t>1552 (94.4%)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>totalco2</t>
+          <t>so2</t>
         </is>
       </c>
     </row>
@@ -1335,17 +1335,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24.9 (5.47)</t>
+          <t>92.9 (3.94)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>23.9 (5.79)</t>
+          <t>96.5 (3.09)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>24.0 (5.75)</t>
+          <t>96.2 (3.33)</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>25.0 [13.0, 43.0]</t>
+          <t>93.0 [88.0, 98.0]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>24.0 [8.00, 50.0]</t>
+          <t>97.0 [79.0, 99.0]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>24.0 [8.00, 50.0]</t>
+          <t>97.0 [79.0, 99.0]</t>
         </is>
       </c>
     </row>
@@ -1379,24 +1379,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>289 (79.0%)</t>
+          <t>300 (97.4%)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1078 (70.4%)</t>
+          <t>1258 (94.2%)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1367 (72.0%)</t>
+          <t>1558 (94.8%)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hematocrit</t>
+          <t>po2</t>
         </is>
       </c>
     </row>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>34.8 (4.46)</t>
+          <t>97.0 (57.3)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>31.9 (5.65)</t>
+          <t>212 (109)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>32.0 (5.63)</t>
+          <t>196 (110)</t>
         </is>
       </c>
     </row>
@@ -1430,17 +1430,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>34.0 [29.3, 41.0]</t>
+          <t>73.0 [33.0, 359]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>32.0 [18.0, 49.5]</t>
+          <t>200 [35.0, 563]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>32.0 [18.0, 49.5]</t>
+          <t>182 [33.0, 563]</t>
         </is>
       </c>
     </row>
@@ -1452,24 +1452,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>355 (97.0%)</t>
+          <t>245 (79.5%)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1223 (79.8%)</t>
+          <t>941 (70.4%)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1578 (83.1%)</t>
+          <t>1186 (72.1%)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>hemoglobin</t>
+          <t>pco2</t>
         </is>
       </c>
     </row>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11.5 (1.57)</t>
+          <t>42.0 (10.9)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10.5 (1.88)</t>
+          <t>42.3 (12.6)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10.6 (1.88)</t>
+          <t>42.2 (12.4)</t>
         </is>
       </c>
     </row>
@@ -1503,17 +1503,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11.4 [9.40, 13.6]</t>
+          <t>41.0 [21.0, 79.0]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>10.5 [5.90, 16.2]</t>
+          <t>41.0 [16.0, 162]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10.6 [5.90, 16.2]</t>
+          <t>41.0 [16.0, 162]</t>
         </is>
       </c>
     </row>
@@ -1525,24 +1525,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>355 (97.0%)</t>
+          <t>245 (79.5%)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1223 (79.8%)</t>
+          <t>941 (70.4%)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1578 (83.1%)</t>
+          <t>1186 (72.1%)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>carboxyhemoglobin</t>
+          <t>fio2</t>
         </is>
       </c>
     </row>
@@ -1554,17 +1554,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NA (NA)</t>
+          <t>85.3 (23.7)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.25 (0.707)</t>
+          <t>57.3 (20.6)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.25 (0.707)</t>
+          <t>59.3 (21.9)</t>
         </is>
       </c>
     </row>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>95.5 [50.0, 100]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.00 [0, 2.00]</t>
+          <t>50.0 [29.0, 100]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.00 [0, 2.00]</t>
+          <t>50.0 [29.0, 100]</t>
         </is>
       </c>
     </row>
@@ -1598,24 +1598,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>366 (100%)</t>
+          <t>304 (98.7%)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1524 (99.5%)</t>
+          <t>1283 (96.0%)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1890 (99.6%)</t>
+          <t>1587 (96.5%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>methemoglobin</t>
+          <t>totalco2</t>
         </is>
       </c>
     </row>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NA (NA)</t>
+          <t>25.4 (5.57)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.833 (0.408)</t>
+          <t>23.6 (5.19)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.833 (0.408)</t>
+          <t>23.9 (5.28)</t>
         </is>
       </c>
     </row>
@@ -1649,17 +1649,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>25.0 [13.0, 43.0]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.00 [0, 1.00]</t>
+          <t>24.0 [8.00, 50.0]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.00 [0, 1.00]</t>
+          <t>24.0 [8.00, 50.0]</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>366 (100%)</t>
+          <t>245 (79.5%)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1526 (99.6%)</t>
+          <t>941 (70.4%)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1892 (99.7%)</t>
+          <t>1186 (72.1%)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>chloride</t>
+          <t>hematocrit</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>103 (3.25)</t>
+          <t>34.6 (4.52)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>107 (4.62)</t>
+          <t>32.0 (5.75)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>106 (4.62)</t>
+          <t>32.1 (5.73)</t>
         </is>
       </c>
     </row>
@@ -1722,17 +1722,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>104 [96.0, 105]</t>
+          <t>34.0 [29.3, 41.0]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>107 [89.0, 123]</t>
+          <t>32.0 [18.0, 49.5]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>107 [89.0, 123]</t>
+          <t>32.0 [18.0, 49.5]</t>
         </is>
       </c>
     </row>
@@ -1744,24 +1744,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>359 (98.1%)</t>
+          <t>299 (97.1%)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1262 (82.4%)</t>
+          <t>1059 (79.3%)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1621 (85.4%)</t>
+          <t>1358 (82.6%)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>hemoglobin</t>
         </is>
       </c>
     </row>
@@ -1773,17 +1773,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.11 (0.0544)</t>
+          <t>11.4 (1.58)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.14 (0.119)</t>
+          <t>10.6 (1.91)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.14 (0.118)</t>
+          <t>10.6 (1.91)</t>
         </is>
       </c>
     </row>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.10 [1.05, 1.21]</t>
+          <t>11.4 [9.40, 13.6]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.13 [0.790, 1.89]</t>
+          <t>10.5 [5.90, 16.2]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.13 [0.790, 1.89]</t>
+          <t>10.6 [5.90, 16.2]</t>
         </is>
       </c>
     </row>
@@ -1817,24 +1817,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>357 (97.5%)</t>
+          <t>299 (97.1%)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1222 (79.8%)</t>
+          <t>1059 (79.3%)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1579 (83.2%)</t>
+          <t>1358 (82.6%)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>carboxyhemoglobin</t>
         </is>
       </c>
     </row>
@@ -1846,17 +1846,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>37.1 (0.458)</t>
+          <t>NA (NA)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>36.8 (1.09)</t>
+          <t>1.25 (0.707)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>36.9 (1.01)</t>
+          <t>1.25 (0.707)</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>36.9 [36.7, 38.0]</t>
+          <t>NA [NA, NA]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>36.8 [34.0, 39.7]</t>
+          <t>1.00 [0, 2.00]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>36.8 [34.0, 39.7]</t>
+          <t>1.00 [0, 2.00]</t>
         </is>
       </c>
     </row>
@@ -1890,24 +1890,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>359 (98.1%)</t>
+          <t>308 (100%)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1496 (97.7%)</t>
+          <t>1328 (99.4%)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1855 (97.7%)</t>
+          <t>1636 (99.5%)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>sodium</t>
+          <t>methemoglobin</t>
         </is>
       </c>
     </row>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>135 (2.99)</t>
+          <t>NA (NA)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>136 (3.43)</t>
+          <t>0.833 (0.408)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>136 (3.42)</t>
+          <t>0.833 (0.408)</t>
         </is>
       </c>
     </row>
@@ -1941,17 +1941,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>137 [130, 139]</t>
+          <t>NA [NA, NA]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>136 [123, 148]</t>
+          <t>1.00 [0, 1.00]</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>136 [123, 148]</t>
+          <t>1.00 [0, 1.00]</t>
         </is>
       </c>
     </row>
@@ -1963,24 +1963,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>359 (98.1%)</t>
+          <t>308 (100%)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1254 (81.9%)</t>
+          <t>1330 (99.6%)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1613 (85.0%)</t>
+          <t>1638 (99.6%)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lactate</t>
+          <t>chloride</t>
         </is>
       </c>
     </row>
@@ -1992,17 +1992,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2.61 (2.02)</t>
+          <t>103 (3.83)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3.08 (2.64)</t>
+          <t>106 (4.69)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3.04 (2.59)</t>
+          <t>106 (4.69)</t>
         </is>
       </c>
     </row>
@@ -2014,17 +2014,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.85 [0.700, 10.3]</t>
+          <t>104 [96.0, 105]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2.10 [0.500, 17.0]</t>
+          <t>107 [89.0, 123]</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2.10 [0.500, 17.0]</t>
+          <t>107 [89.0, 123]</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>326 (89.1%)</t>
+          <t>303 (98.4%)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1166 (76.1%)</t>
+          <t>1095 (82.0%)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1492 (78.6%)</t>
+          <t>1398 (85.0%)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>glucose</t>
+          <t>calcium</t>
         </is>
       </c>
     </row>
@@ -2065,17 +2065,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>168 (61.5)</t>
+          <t>1.12 (0.0570)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>167 (55.6)</t>
+          <t>1.14 (0.122)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>167 (55.6)</t>
+          <t>1.14 (0.121)</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>135 [105, 267]</t>
+          <t>1.10 [1.05, 1.21]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>163 [25.0, 418]</t>
+          <t>1.13 [0.790, 1.89]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>162 [25.0, 418]</t>
+          <t>1.13 [0.790, 1.89]</t>
         </is>
       </c>
     </row>
@@ -2109,24 +2109,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>358 (97.8%)</t>
+          <t>301 (97.7%)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1223 (79.8%)</t>
+          <t>1062 (79.5%)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1581 (83.3%)</t>
+          <t>1363 (82.9%)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>sapsii</t>
+          <t>temperature</t>
         </is>
       </c>
     </row>
@@ -2138,17 +2138,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>41.5 (13.8)</t>
+          <t>37.1 (0.471)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>49.2 (16.3)</t>
+          <t>36.8 (1.11)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>47.7 (16.1)</t>
+          <t>36.9 (1.04)</t>
         </is>
       </c>
     </row>
@@ -2160,68 +2160,360 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>40.0 [10.0, 115]</t>
+          <t>37.0 [36.7, 38.0]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>46.0 [8.00, 113]</t>
+          <t>36.7 [34.0, 39.7]</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>45.0 [8.00, 115]</t>
+          <t>36.8 [34.0, 39.7]</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>pressor</t>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>302 (98.1%)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1304 (97.6%)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1606 (97.7%)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>348 (95.1%)</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>944 (61.6%)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>1292 (68.1%)</t>
+          <t>sodium</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>135 (3.51)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>136 (3.52)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>136 (3.51)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Median [Min, Max]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>137 [130, 139]</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>136 [123, 148]</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>136 [123, 148]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>303 (98.4%)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1088 (81.4%)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1391 (84.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>lactate</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2.51 (2.09)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3.00 (2.59)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2.96 (2.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Median [Min, Max]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1.80 [0.700, 10.3]</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2.10 [0.500, 17.0]</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2.00 [0.500, 17.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>274 (89.0%)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1011 (75.7%)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1285 (78.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>glucose</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>164 (66.2)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>165 (55.0)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>165 (55.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Median [Min, Max]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>133 [105, 267]</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>160 [25.0, 418]</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>160 [25.0, 418]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>302 (98.1%)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1059 (79.3%)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1361 (82.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>sapsii</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>41.4 (14.1)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>48.9 (16.3)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>47.5 (16.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Median [Min, Max]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>40.0 [10.0, 115]</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>46.0 [8.00, 113]</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>45.0 [8.00, 115]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>pressor</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>281 (91.2%)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>726 (54.3%)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1007 (61.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>18 (4.9%)</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>588 (38.4%)</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>606 (31.9%)</t>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>27 (8.8%)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>610 (45.7%)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>637 (38.7%)</t>
         </is>
       </c>
     </row>

--- a/table-1b.xlsx
+++ b/table-1b.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tracheostomy/InvasiveVent(N=1336)</t>
+          <t>Tracheostomy/InvasiveVent(N=1340)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Overall(N=1644)</t>
+          <t>Overall(N=1648)</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.20 (3.82)</t>
+          <t>2.19 (3.81)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>505 (37.8%)</t>
+          <t>506 (37.8%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>606 (36.9%)</t>
+          <t>607 (36.8%)</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.54 (1.27)</t>
+          <t>1.54 (1.26)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>174 (106)</t>
+          <t>175 (106)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1245 (93.2%)</t>
+          <t>1249 (93.2%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1546 (94.0%)</t>
+          <t>1550 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7.40 (0.0818)</t>
+          <t>7.40 (0.0817)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.40 (0.0808)</t>
+          <t>7.40 (0.0807)</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>157 (11.8%)</t>
+          <t>158 (11.8%)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>209 (12.7%)</t>
+          <t>210 (12.7%)</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23.2 (4.52)</t>
+          <t>23.2 (4.51)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23.5 (4.71)</t>
+          <t>23.5 (4.70)</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1180 (88.3%)</t>
+          <t>1184 (88.4%)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1449 (88.1%)</t>
+          <t>1453 (88.2%)</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>950 (71.1%)</t>
+          <t>954 (71.2%)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1218 (74.1%)</t>
+          <t>1222 (74.2%)</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>93.3 (3.94)</t>
+          <t>85.8 (14.3)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>96.3 (2.85)</t>
+          <t>89.9 (15.0)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>96.0 (3.02)</t>
+          <t>89.5 (14.9)</t>
         </is>
       </c>
     </row>
@@ -1211,17 +1211,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>94.0 [88.0, 98.0]</t>
+          <t>92.0 [48.0, 98.0]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>97.0 [79.0, 99.0]</t>
+          <t>96.0 [30.0, 99.0]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>97.0 [79.0, 99.0]</t>
+          <t>96.0 [30.0, 99.0]</t>
         </is>
       </c>
     </row>
@@ -1233,17 +1233,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>299 (97.1%)</t>
+          <t>289 (93.8%)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1220 (91.3%)</t>
+          <t>1180 (88.1%)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1519 (92.4%)</t>
+          <t>1469 (89.1%)</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>134 (95.1)</t>
+          <t>119 (82.5)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>324 (130)</t>
+          <t>305 (142)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>309 (137)</t>
+          <t>288 (148)</t>
         </is>
       </c>
     </row>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>114 [65.6, 342]</t>
+          <t>101 [50.0, 342]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>323 [64.1, 575]</t>
+          <t>311 [41.5, 575]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>313 [64.1, 575]</t>
+          <t>301 [41.5, 575]</t>
         </is>
       </c>
     </row>
@@ -1306,17 +1306,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>301 (97.7%)</t>
+          <t>298 (96.8%)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1251 (93.6%)</t>
+          <t>1242 (92.7%)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1552 (94.4%)</t>
+          <t>1540 (93.4%)</t>
         </is>
       </c>
     </row>
@@ -1335,17 +1335,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>92.9 (3.94)</t>
+          <t>87.3 (13.8)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>96.5 (3.09)</t>
+          <t>88.6 (17.0)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>96.2 (3.33)</t>
+          <t>88.5 (16.6)</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>93.0 [88.0, 98.0]</t>
+          <t>92.0 [48.0, 98.0]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>97.0 [79.0, 99.0]</t>
+          <t>97.0 [30.0, 99.0]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>97.0 [79.0, 99.0]</t>
+          <t>96.0 [30.0, 99.0]</t>
         </is>
       </c>
     </row>
@@ -1379,17 +1379,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>300 (97.4%)</t>
+          <t>293 (95.1%)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1258 (94.2%)</t>
+          <t>1228 (91.6%)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1558 (94.8%)</t>
+          <t>1521 (92.3%)</t>
         </is>
       </c>
     </row>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>97.0 (57.3)</t>
+          <t>101 (60.7)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>212 (109)</t>
+          <t>182 (110)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>196 (110)</t>
+          <t>165 (107)</t>
         </is>
       </c>
     </row>
@@ -1430,17 +1430,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>73.0 [33.0, 359]</t>
+          <t>80.0 [26.0, 359]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>200 [35.0, 563]</t>
+          <t>168 [12.0, 563]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>182 [33.0, 563]</t>
+          <t>143 [12.0, 563]</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>245 (79.5%)</t>
+          <t>171 (55.5%)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>941 (70.4%)</t>
+          <t>816 (60.9%)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1186 (72.1%)</t>
+          <t>987 (59.9%)</t>
         </is>
       </c>
     </row>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>42.0 (10.9)</t>
+          <t>42.2 (12.4)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>42.3 (12.6)</t>
+          <t>43.6 (14.8)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>42.2 (12.4)</t>
+          <t>43.3 (14.3)</t>
         </is>
       </c>
     </row>
@@ -1503,17 +1503,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>41.0 [21.0, 79.0]</t>
+          <t>41.0 [21.0, 111]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>41.0 [16.0, 162]</t>
+          <t>41.0 [14.0, 162]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>41.0 [16.0, 162]</t>
+          <t>41.0 [14.0, 162]</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1525,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>245 (79.5%)</t>
+          <t>173 (56.2%)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>941 (70.4%)</t>
+          <t>816 (60.9%)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1186 (72.1%)</t>
+          <t>989 (60.0%)</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>57.3 (20.6)</t>
+          <t>60.4 (22.3)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>59.3 (21.9)</t>
+          <t>62.0 (23.0)</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1283 (96.0%)</t>
+          <t>1280 (95.5%)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1587 (96.5%)</t>
+          <t>1584 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25.4 (5.57)</t>
+          <t>25.3 (5.49)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>23.6 (5.19)</t>
+          <t>23.6 (6.02)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>23.9 (5.28)</t>
+          <t>24.0 (5.95)</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>24.0 [8.00, 50.0]</t>
+          <t>24.0 [4.00, 60.0]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>24.0 [8.00, 50.0]</t>
+          <t>24.0 [4.00, 60.0]</t>
         </is>
       </c>
     </row>
@@ -1671,17 +1671,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>245 (79.5%)</t>
+          <t>173 (56.2%)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>941 (70.4%)</t>
+          <t>816 (60.9%)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1186 (72.1%)</t>
+          <t>989 (60.0%)</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>34.6 (4.52)</t>
+          <t>36.5 (4.88)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>32.0 (5.75)</t>
+          <t>31.8 (5.80)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>32.1 (5.73)</t>
+          <t>31.9 (5.83)</t>
         </is>
       </c>
     </row>
@@ -1722,17 +1722,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>34.0 [29.3, 41.0]</t>
+          <t>37.5 [30.0, 44.7]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>32.0 [18.0, 49.5]</t>
+          <t>32.0 [12.0, 49.5]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>32.0 [18.0, 49.5]</t>
+          <t>32.0 [12.0, 49.5]</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>299 (97.1%)</t>
+          <t>298 (96.8%)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1059 (79.3%)</t>
+          <t>1046 (78.1%)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1358 (82.6%)</t>
+          <t>1344 (81.6%)</t>
         </is>
       </c>
     </row>
@@ -1773,17 +1773,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11.4 (1.58)</t>
+          <t>12.0 (1.63)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10.6 (1.91)</t>
+          <t>10.5 (1.93)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10.6 (1.91)</t>
+          <t>10.5 (1.94)</t>
         </is>
       </c>
     </row>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11.4 [9.40, 13.6]</t>
+          <t>12.3 [9.70, 14.6]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10.5 [5.90, 16.2]</t>
+          <t>10.5 [3.90, 16.2]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10.6 [5.90, 16.2]</t>
+          <t>10.5 [3.90, 16.2]</t>
         </is>
       </c>
     </row>
@@ -1817,17 +1817,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>299 (97.1%)</t>
+          <t>298 (96.8%)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1059 (79.3%)</t>
+          <t>1046 (78.1%)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1358 (82.6%)</t>
+          <t>1344 (81.6%)</t>
         </is>
       </c>
     </row>
@@ -1846,17 +1846,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NA (NA)</t>
+          <t>2.00 (NA)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1.25 (0.707)</t>
+          <t>1.82 (1.17)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.25 (0.707)</t>
+          <t>1.83 (1.11)</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>2.00 [2.00, 2.00]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.00 [0, 2.00]</t>
+          <t>2.00 [0, 4.00]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.00 [0, 2.00]</t>
+          <t>2.00 [0, 4.00]</t>
         </is>
       </c>
     </row>
@@ -1890,17 +1890,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>308 (100%)</t>
+          <t>307 (99.7%)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1328 (99.4%)</t>
+          <t>1329 (99.2%)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1636 (99.5%)</t>
+          <t>1636 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NA (NA)</t>
+          <t>1.00 (NA)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.833 (0.408)</t>
+          <t>0.600 (0.516)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.833 (0.408)</t>
+          <t>0.636 (0.505)</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>308 (100%)</t>
+          <t>307 (99.7%)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1330 (99.6%)</t>
+          <t>1330 (99.3%)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1638 (99.6%)</t>
+          <t>1637 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -1992,17 +1992,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>103 (3.83)</t>
+          <t>101 (5.62)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>106 (4.69)</t>
+          <t>106 (4.64)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>106 (4.69)</t>
+          <t>106 (4.73)</t>
         </is>
       </c>
     </row>
@@ -2014,17 +2014,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>104 [96.0, 105]</t>
+          <t>104 [91.0, 105]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>107 [89.0, 123]</t>
+          <t>106 [89.0, 123]</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>107 [89.0, 123]</t>
+          <t>106 [89.0, 123]</t>
         </is>
       </c>
     </row>
@@ -2036,17 +2036,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>303 (98.4%)</t>
+          <t>301 (97.7%)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1095 (82.0%)</t>
+          <t>1088 (81.2%)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1398 (85.0%)</t>
+          <t>1389 (84.3%)</t>
         </is>
       </c>
     </row>
@@ -2065,17 +2065,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.12 (0.0570)</t>
+          <t>1.14 (0.0765)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>1.14 (0.124)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>1.14 (0.122)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1.14 (0.121)</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.10 [1.05, 1.21]</t>
+          <t>1.11 [1.05, 1.28]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.13 [0.790, 1.89]</t>
+          <t>1.13 [0.760, 1.89]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.13 [0.790, 1.89]</t>
+          <t>1.13 [0.760, 1.89]</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2109,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>301 (97.7%)</t>
+          <t>300 (97.4%)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1062 (79.5%)</t>
+          <t>1054 (78.7%)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1363 (82.9%)</t>
+          <t>1354 (82.2%)</t>
         </is>
       </c>
     </row>
@@ -2138,17 +2138,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>37.1 (0.471)</t>
+          <t>37.4 (0.898)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>36.8 (1.11)</t>
+          <t>36.8 (1.07)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>36.9 (1.04)</t>
+          <t>36.9 (1.06)</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>37.0 [36.7, 38.0]</t>
+          <t>36.9 [36.6, 39.4]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>302 (98.1%)</t>
+          <t>297 (96.4%)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1304 (97.6%)</t>
+          <t>1301 (97.1%)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1606 (97.7%)</t>
+          <t>1598 (97.0%)</t>
         </is>
       </c>
     </row>
@@ -2211,17 +2211,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>135 (3.51)</t>
+          <t>135 (6.37)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>136 (3.52)</t>
+          <t>136 (3.48)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>136 (3.51)</t>
+          <t>136 (3.59)</t>
         </is>
       </c>
     </row>
@@ -2233,17 +2233,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>137 [130, 139]</t>
+          <t>137 [122, 142]</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>136 [123, 148]</t>
+          <t>136 [123, 145]</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>136 [123, 148]</t>
+          <t>136 [122, 145]</t>
         </is>
       </c>
     </row>
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>303 (98.4%)</t>
+          <t>300 (97.4%)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1088 (81.4%)</t>
+          <t>1080 (80.6%)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1391 (84.6%)</t>
+          <t>1380 (83.7%)</t>
         </is>
       </c>
     </row>
@@ -2284,17 +2284,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2.51 (2.09)</t>
+          <t>2.42 (1.65)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.00 (2.59)</t>
+          <t>3.32 (2.95)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2.96 (2.55)</t>
+          <t>3.16 (2.78)</t>
         </is>
       </c>
     </row>
@@ -2306,17 +2306,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.80 [0.700, 10.3]</t>
+          <t>1.85 [0.700, 10.3]</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2.10 [0.500, 17.0]</t>
+          <t>2.20 [0.500, 22.0]</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2.00 [0.500, 17.0]</t>
+          <t>2.10 [0.500, 22.0]</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>274 (89.0%)</t>
+          <t>220 (71.4%)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1011 (75.7%)</t>
+          <t>925 (69.0%)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1285 (78.2%)</t>
+          <t>1145 (69.5%)</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>164 (66.2)</t>
+          <t>156 (55.4)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
+          <t>166 (55.1)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>165 (55.0)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>165 (55.1)</t>
         </is>
       </c>
     </row>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>133 [105, 267]</t>
+          <t>131 [105, 267]</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>160 [25.0, 418]</t>
+          <t>161 [25.0, 418]</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160 [25.0, 418]</t>
+          <t>161 [25.0, 418]</t>
         </is>
       </c>
     </row>
@@ -2401,17 +2401,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>302 (98.1%)</t>
+          <t>299 (97.1%)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1059 (79.3%)</t>
+          <t>1045 (78.0%)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1361 (82.8%)</t>
+          <t>1344 (81.6%)</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>726 (54.3%)</t>
+          <t>730 (54.5%)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1007 (61.3%)</t>
+          <t>1011 (61.3%)</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>610 (45.7%)</t>
+          <t>610 (45.5%)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
